--- a/data/trans_dic/P16A_2_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,03; 37,71</t>
+          <t>30,26; 37,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,05; 62,51</t>
+          <t>56,36; 62,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,79; 51,42</t>
+          <t>46,79; 51,54</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 23,5</t>
+          <t>14,38; 23,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,24; 57,11</t>
+          <t>32,13; 53,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,2; 40,38</t>
+          <t>24,38; 40,03</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,16; 23,07</t>
+          <t>16,3; 23,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,82; 32,2</t>
+          <t>26,15; 32,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,16; 26,77</t>
+          <t>22,0; 26,72</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,58; 24,56</t>
+          <t>17,26; 24,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,35; 52,34</t>
+          <t>37,33; 52,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,91; 39,07</t>
+          <t>28,79; 38,32</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>154658; 194177</t>
+          <t>155822; 194543</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>431010; 472272</t>
+          <t>425820; 470787</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>594469; 653229</t>
+          <t>594487; 654772</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>319813; 538135</t>
+          <t>329392; 537788</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>721549; 1277938</t>
+          <t>718916; 1194780</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1140902; 1828461</t>
+          <t>1103784; 1812418</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>104500; 149159</t>
+          <t>105392; 150066</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>170539; 212639</t>
+          <t>172697; 213359</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>289619; 349884</t>
+          <t>287562; 349212</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>606901; 847629</t>
+          <t>595630; 847207</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1364622; 1912429</t>
+          <t>1364056; 1907600</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2054571; 2776051</t>
+          <t>2045475; 2723080</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_2_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>47,95%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,26; 37,78</t>
+          <t>28,73; 36,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,36; 62,31</t>
+          <t>56,41; 61,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,79; 51,54</t>
+          <t>45,4; 50,04</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,38; 23,48</t>
+          <t>20,47; 24,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,13; 53,39</t>
+          <t>32,32; 36,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,38; 40,03</t>
+          <t>26,97; 29,77</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,3; 23,21</t>
+          <t>16,46; 23,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,15; 32,3</t>
+          <t>25,79; 31,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,0; 26,72</t>
+          <t>21,93; 26,17</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 24,54</t>
+          <t>22,06; 25,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,33; 52,21</t>
+          <t>37,17; 39,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,79; 38,32</t>
+          <t>30,18; 32,19</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>173541</t>
+          <t>187090</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>449881</t>
+          <t>484423</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>623422</t>
+          <t>671513</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>155822; 194543</t>
+          <t>166207; 209223</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>425820; 470787</t>
+          <t>463693; 506797</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>594487; 654772</t>
+          <t>635907; 700868</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>467018</t>
+          <t>502140</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>876718</t>
+          <t>741359</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1343736</t>
+          <t>1243500</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>329392; 537788</t>
+          <t>456577; 549763</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>718916; 1194780</t>
+          <t>701824; 781740</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1103784; 1812418</t>
+          <t>1187413; 1310611</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>125156</t>
+          <t>137511</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>192288</t>
+          <t>210566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317444</t>
+          <t>348077</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>105392; 150066</t>
+          <t>117136; 163727</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>172697; 213359</t>
+          <t>189519; 234889</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>287562; 349212</t>
+          <t>317274; 378580</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>765715</t>
+          <t>826742</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1518887</t>
+          <t>1436347</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2284603</t>
+          <t>2263090</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>595630; 847207</t>
+          <t>776710; 881285</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1364056; 1907600</t>
+          <t>1385671; 1489252</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2045475; 2723080</t>
+          <t>2187628; 2333372</t>
         </is>
       </c>
     </row>
